--- a/outputs/benchmark-beaters/Benchmark_Beaters_2026-07-27.xlsx
+++ b/outputs/benchmark-beaters/Benchmark_Beaters_2026-07-27.xlsx
@@ -19,7 +19,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Cdn Hardcoded'!$A$1:$J$26</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Cdn'!$A$1:$J$48</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'US Hardcoded'!$A$1:$J$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'US Hardcoded'!$A$1:$J$47</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'US'!$A$1:$J$54</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -383,7 +383,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -558,11 +558,35 @@
         <color rgb="FFC67A29"/>
       </bottom>
     </border>
+    <border>
+      <left style="medium">
+        <color theme="2"/>
+      </left>
+      <right style="medium">
+        <color theme="2"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="2"/>
+      </left>
+      <right style="medium">
+        <color theme="2"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color theme="2"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="152">
+  <cellXfs count="153">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -963,6 +987,7 @@
     <xf numFmtId="0" fontId="33" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2086,7 +2111,7 @@
     <row r="2" ht="15.6" customHeight="1">
       <c r="A2" s="22" t="n"/>
       <c r="B2" s="21" t="n">
-        <v>46230.56563682047</v>
+        <v>46230.8070455554</v>
       </c>
       <c r="C2" s="22" t="n"/>
     </row>
@@ -2148,7 +2173,7 @@
         </is>
       </c>
       <c r="H2" s="84" t="n">
-        <v>46230.56563682047</v>
+        <v>46230.8070455554</v>
       </c>
       <c r="J2" s="83" t="n"/>
     </row>
@@ -2281,10 +2306,10 @@
         </is>
       </c>
       <c r="G8" s="118" t="n">
-        <v>0.441</v>
+        <v>0.409</v>
       </c>
       <c r="H8" s="119" t="n">
-        <v>7850.04</v>
+        <v>7816.25</v>
       </c>
       <c r="I8" s="120" t="inlineStr">
         <is>
@@ -2322,10 +2347,10 @@
         </is>
       </c>
       <c r="G9" s="118" t="n">
-        <v>0.271</v>
+        <v>0.162</v>
       </c>
       <c r="H9" s="124" t="n">
-        <v>2215.94</v>
+        <v>2145.48</v>
       </c>
       <c r="I9" s="125" t="inlineStr">
         <is>
@@ -2363,10 +2388,10 @@
         </is>
       </c>
       <c r="G10" s="118" t="n">
-        <v>0.773</v>
+        <v>0.761</v>
       </c>
       <c r="H10" s="119" t="n">
-        <v>1565.38</v>
+        <v>1924.02</v>
       </c>
       <c r="I10" s="120" t="inlineStr">
         <is>
@@ -2404,10 +2429,10 @@
         </is>
       </c>
       <c r="G11" s="118" t="n">
-        <v>0.481</v>
+        <v>0.434</v>
       </c>
       <c r="H11" s="124" t="n">
-        <v>2385.76</v>
+        <v>2667.47</v>
       </c>
       <c r="I11" s="125" t="inlineStr">
         <is>
@@ -2445,10 +2470,10 @@
         </is>
       </c>
       <c r="G12" s="118" t="n">
-        <v>0.382</v>
+        <v>0.375</v>
       </c>
       <c r="H12" s="119" t="n">
-        <v>38174.66</v>
+        <v>40943.84</v>
       </c>
       <c r="I12" s="120" t="inlineStr">
         <is>
@@ -2467,39 +2492,39 @@
       </c>
       <c r="C13" s="121" t="inlineStr">
         <is>
-          <t>ARG</t>
+          <t>PPL</t>
         </is>
       </c>
       <c r="D13" s="122" t="inlineStr">
         <is>
-          <t>Amerigo Resources Ltd.</t>
+          <t>Pembina Pipeline Corporation</t>
         </is>
       </c>
       <c r="E13" s="123" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F13" s="123" t="inlineStr">
         <is>
-          <t>Metals and Mining</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G13" s="118" t="n">
-        <v>0.292</v>
+        <v>0.276</v>
       </c>
       <c r="H13" s="124" t="n">
-        <v>681.6799999999999</v>
+        <v>29189.48</v>
       </c>
       <c r="I13" s="125" t="inlineStr">
         <is>
-          <t>Amerigo Resources Ltd through its subsidiary Minera Valle Central S</t>
+          <t>Pembina Pipeline Corporation provides energy transportation and midstream services</t>
         </is>
       </c>
       <c r="J13" s="54" t="n"/>
       <c r="K13" s="28" t="n"/>
     </row>
-    <row r="14" ht="52" customHeight="1">
+    <row r="14" ht="70" customHeight="1">
       <c r="A14" s="36" t="n"/>
       <c r="B14" s="127" t="inlineStr">
         <is>
@@ -2508,39 +2533,39 @@
       </c>
       <c r="C14" s="115" t="inlineStr">
         <is>
-          <t>PPL</t>
+          <t>CU</t>
         </is>
       </c>
       <c r="D14" s="116" t="inlineStr">
         <is>
-          <t>Pembina Pipeline Corporation</t>
+          <t>Canadian Utilities Limited</t>
         </is>
       </c>
       <c r="E14" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F14" s="117" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Multi-Utilities</t>
         </is>
       </c>
       <c r="G14" s="118" t="n">
-        <v>0.286</v>
+        <v>0.276</v>
       </c>
       <c r="H14" s="119" t="n">
-        <v>28518.97</v>
+        <v>10629.48</v>
       </c>
       <c r="I14" s="120" t="inlineStr">
         <is>
-          <t>Pembina Pipeline Corporation provides energy transportation and midstream services</t>
+          <t>Canadian Utilities Limited together with its subsidiaries engages in the electricity natural gas renewables pipelines and liquids businesses in Canada Australia and internationally</t>
         </is>
       </c>
       <c r="J14" s="53" t="n"/>
       <c r="K14" s="36" t="n"/>
     </row>
-    <row r="15" ht="70" customHeight="1">
+    <row r="15" ht="52" customHeight="1">
       <c r="A15" s="28" t="n"/>
       <c r="B15" s="127" t="inlineStr">
         <is>
@@ -2549,33 +2574,33 @@
       </c>
       <c r="C15" s="121" t="inlineStr">
         <is>
-          <t>CU</t>
+          <t>ARG</t>
         </is>
       </c>
       <c r="D15" s="122" t="inlineStr">
         <is>
-          <t>Canadian Utilities Limited</t>
+          <t>Amerigo Resources Ltd.</t>
         </is>
       </c>
       <c r="E15" s="123" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F15" s="123" t="inlineStr">
         <is>
-          <t>Multi-Utilities</t>
+          <t>Metals and Mining</t>
         </is>
       </c>
       <c r="G15" s="118" t="n">
-        <v>0.274</v>
+        <v>0.264</v>
       </c>
       <c r="H15" s="124" t="n">
-        <v>10045.65</v>
+        <v>845.1</v>
       </c>
       <c r="I15" s="125" t="inlineStr">
         <is>
-          <t>Canadian Utilities Limited together with its subsidiaries engages in the electricity natural gas renewables pipelines and liquids businesses in Canada Australia and internationally</t>
+          <t>Amerigo Resources Ltd through its subsidiary Minera Valle Central S</t>
         </is>
       </c>
       <c r="J15" s="54" t="n"/>
@@ -2609,10 +2634,10 @@
         </is>
       </c>
       <c r="G16" s="118" t="n">
-        <v>0.257</v>
+        <v>0.239</v>
       </c>
       <c r="H16" s="119" t="n">
-        <v>576.85</v>
+        <v>703.8</v>
       </c>
       <c r="I16" s="120" t="inlineStr">
         <is>
@@ -2622,7 +2647,7 @@
       <c r="J16" s="54" t="n"/>
       <c r="K16" s="28" t="n"/>
     </row>
-    <row r="17" ht="70" customHeight="1">
+    <row r="17" ht="88" customHeight="1">
       <c r="A17" s="36" t="n"/>
       <c r="B17" s="127" t="inlineStr">
         <is>
@@ -2631,39 +2656,39 @@
       </c>
       <c r="C17" s="121" t="inlineStr">
         <is>
-          <t>MFC</t>
+          <t>TOY</t>
         </is>
       </c>
       <c r="D17" s="122" t="inlineStr">
         <is>
-          <t>Manulife Financial Corporation</t>
+          <t>Spin Master Corp.</t>
         </is>
       </c>
       <c r="E17" s="123" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F17" s="123" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Leisure Products</t>
         </is>
       </c>
       <c r="G17" s="118" t="n">
-        <v>0.236</v>
+        <v>0.23</v>
       </c>
       <c r="H17" s="124" t="n">
-        <v>65572.44</v>
+        <v>1621.94</v>
       </c>
       <c r="I17" s="125" t="inlineStr">
         <is>
-          <t>Manulife Financial Corporation together with its subsidiaries provides financial products and services in the United States Canada Asia and internationally</t>
+          <t>Spin Master Corp a children’s entertainment company engages in the creation design manufacture licensing and marketing of various toys entertainment products and digital games in North America Europe and internationally</t>
         </is>
       </c>
       <c r="J17" s="53" t="n"/>
       <c r="K17" s="36" t="n"/>
     </row>
-    <row r="18" ht="88" customHeight="1">
+    <row r="18" ht="70" customHeight="1">
       <c r="A18" s="28" t="n"/>
       <c r="B18" s="127" t="inlineStr">
         <is>
@@ -2672,33 +2697,33 @@
       </c>
       <c r="C18" s="115" t="inlineStr">
         <is>
-          <t>TOY</t>
+          <t>MFC</t>
         </is>
       </c>
       <c r="D18" s="116" t="inlineStr">
         <is>
-          <t>Spin Master Corp.</t>
+          <t>Manulife Financial Corporation</t>
         </is>
       </c>
       <c r="E18" s="117" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F18" s="117" t="inlineStr">
         <is>
-          <t>Leisure Products</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="G18" s="118" t="n">
-        <v>0.236</v>
+        <v>0.217</v>
       </c>
       <c r="H18" s="119" t="n">
-        <v>1330.28</v>
+        <v>73319.98</v>
       </c>
       <c r="I18" s="120" t="inlineStr">
         <is>
-          <t>Spin Master Corp a children’s entertainment company engages in the creation design manufacture licensing and marketing of various toys entertainment products and digital games in North America Europe and internationally</t>
+          <t>Manulife Financial Corporation together with its subsidiaries provides financial products and services in the United States Canada Asia and internationally</t>
         </is>
       </c>
       <c r="J18" s="54" t="n"/>
@@ -2732,10 +2757,10 @@
         </is>
       </c>
       <c r="G19" s="118" t="n">
-        <v>1.263</v>
+        <v>1.252</v>
       </c>
       <c r="H19" s="124" t="n">
-        <v>284.57</v>
+        <v>365.09</v>
       </c>
       <c r="I19" s="125" t="inlineStr">
         <is>
@@ -2773,10 +2798,10 @@
         </is>
       </c>
       <c r="G20" s="118" t="n">
-        <v>0.538</v>
+        <v>0.54</v>
       </c>
       <c r="H20" s="119" t="n">
-        <v>1892.54</v>
+        <v>2189.94</v>
       </c>
       <c r="I20" s="120" t="inlineStr">
         <is>
@@ -2786,7 +2811,7 @@
       <c r="J20" s="54" t="n"/>
       <c r="K20" s="28" t="n"/>
     </row>
-    <row r="21" ht="70" customHeight="1">
+    <row r="21" ht="124" customHeight="1">
       <c r="A21" s="36" t="n"/>
       <c r="B21" s="128" t="inlineStr">
         <is>
@@ -2795,39 +2820,39 @@
       </c>
       <c r="C21" s="121" t="inlineStr">
         <is>
-          <t>KBL</t>
+          <t>SLF</t>
         </is>
       </c>
       <c r="D21" s="122" t="inlineStr">
         <is>
-          <t>K-Bro Linen Inc.</t>
+          <t>Sun Life Financial Inc.</t>
         </is>
       </c>
       <c r="E21" s="123" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F21" s="123" t="inlineStr">
         <is>
-          <t>Commercial Services and Supplies</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="G21" s="118" t="n">
-        <v>0.419</v>
+        <v>0.39</v>
       </c>
       <c r="H21" s="124" t="n">
-        <v>390.27</v>
+        <v>46289</v>
       </c>
       <c r="I21" s="125" t="inlineStr">
         <is>
-          <t>K-Bro Linen Inc together with its subsidiaries provides laundry and linen services to healthcare organizations hotels and other commercial accounts in Canada and the United Kingdom</t>
+          <t>Sun Life Financial Inc a financial services company provides asset management wealth insurance and health solutions to individual and institutional customers in Canada the United States the United Kingdom Ireland Hong Kong the Philippines Japan Indonesia India China Australia Singapore Vietnam Malaysia and Bermuda</t>
         </is>
       </c>
       <c r="J21" s="53" t="n"/>
       <c r="K21" s="36" t="n"/>
     </row>
-    <row r="22" ht="124" customHeight="1">
+    <row r="22" ht="70" customHeight="1">
       <c r="A22" s="28" t="n"/>
       <c r="B22" s="128" t="inlineStr">
         <is>
@@ -2836,39 +2861,39 @@
       </c>
       <c r="C22" s="115" t="inlineStr">
         <is>
-          <t>SLF</t>
+          <t>CNR</t>
         </is>
       </c>
       <c r="D22" s="116" t="inlineStr">
         <is>
-          <t>Sun Life Financial Inc.</t>
+          <t>Canadian National Railway Company</t>
         </is>
       </c>
       <c r="E22" s="117" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F22" s="117" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Ground Transportation</t>
         </is>
       </c>
       <c r="G22" s="118" t="n">
-        <v>0.393</v>
+        <v>0.356</v>
       </c>
       <c r="H22" s="119" t="n">
-        <v>41467.31</v>
+        <v>78116.71000000001</v>
       </c>
       <c r="I22" s="120" t="inlineStr">
         <is>
-          <t>Sun Life Financial Inc a financial services company provides asset management wealth insurance and health solutions to individual and institutional customers in Canada the United States the United Kingdom Ireland Hong Kong the Philippines Japan Indonesia India China Australia Singapore Vietnam Malaysia and Bermuda</t>
+          <t>Canadian National Railway Company together with its subsidiaries engages in the rail intermodal trucking and related transportation businesses in Canada and the United States</t>
         </is>
       </c>
       <c r="J22" s="54" t="n"/>
       <c r="K22" s="28" t="n"/>
     </row>
-    <row r="23" ht="70" customHeight="1">
+    <row r="23" ht="52" customHeight="1">
       <c r="A23" s="28" t="n"/>
       <c r="B23" s="129" t="inlineStr">
         <is>
@@ -2877,33 +2902,33 @@
       </c>
       <c r="C23" s="130" t="inlineStr">
         <is>
-          <t>CNR</t>
+          <t>DFY</t>
         </is>
       </c>
       <c r="D23" s="131" t="inlineStr">
         <is>
-          <t>Canadian National Railway Company</t>
+          <t>Definity Financial Corporation</t>
         </is>
       </c>
       <c r="E23" s="132" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F23" s="132" t="inlineStr">
         <is>
-          <t>Ground Transportation</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="G23" s="133" t="n">
-        <v>0.38</v>
+        <v>0.197</v>
       </c>
       <c r="H23" s="134" t="n">
-        <v>72839.50999999999</v>
+        <v>6877.44</v>
       </c>
       <c r="I23" s="135" t="inlineStr">
         <is>
-          <t>Canadian National Railway Company together with its subsidiaries engages in the rail intermodal trucking and related transportation businesses in Canada and the United States</t>
+          <t>Definity Financial Corporation together with its subsidiaries offers property and casualty insurance products in Canada</t>
         </is>
       </c>
       <c r="J23" s="54" t="n"/>
@@ -4244,7 +4269,7 @@
         </is>
       </c>
       <c r="H2" s="84" t="n">
-        <v>46230.56563682047</v>
+        <v>46230.8070455554</v>
       </c>
       <c r="J2" s="83" t="n"/>
     </row>
@@ -4377,10 +4402,10 @@
         </is>
       </c>
       <c r="G8" s="118" t="n">
-        <v>0.415</v>
+        <v>0.399</v>
       </c>
       <c r="H8" s="119" t="n">
-        <v>16769.06</v>
+        <v>17248.28</v>
       </c>
       <c r="I8" s="120" t="inlineStr">
         <is>
@@ -4418,10 +4443,10 @@
         </is>
       </c>
       <c r="G9" s="118" t="n">
-        <v>0.401</v>
+        <v>0.377</v>
       </c>
       <c r="H9" s="124" t="n">
-        <v>100601.02</v>
+        <v>114863.66</v>
       </c>
       <c r="I9" s="125" t="inlineStr">
         <is>
@@ -4431,7 +4456,7 @@
       <c r="J9" s="54" t="n"/>
       <c r="K9" s="28" t="n"/>
     </row>
-    <row r="10" ht="70" customHeight="1">
+    <row r="10" ht="88" customHeight="1">
       <c r="A10" s="36" t="n"/>
       <c r="B10" s="126" t="inlineStr">
         <is>
@@ -4440,33 +4465,33 @@
       </c>
       <c r="C10" s="115" t="inlineStr">
         <is>
-          <t>VTR</t>
+          <t>VTRS</t>
         </is>
       </c>
       <c r="D10" s="116" t="inlineStr">
         <is>
-          <t>Ventas Inc.</t>
+          <t>Viatris Inc.</t>
         </is>
       </c>
       <c r="E10" s="117" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F10" s="117" t="inlineStr">
         <is>
-          <t>Health Care REITs</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="G10" s="118" t="n">
-        <v>0.335</v>
+        <v>0.374</v>
       </c>
       <c r="H10" s="119" t="n">
-        <v>41077.71</v>
+        <v>20595.11</v>
       </c>
       <c r="I10" s="120" t="inlineStr">
         <is>
-          <t>Ventas Inc is a leading S&amp;P 500 real estate investment trust enabling exceptional environments that benefit a large and growing aging population</t>
+          <t>Viatris Inc together with its subsidiaries operates as a healthcare company in North America Europe China Taiwan Hong Kong Japan Australia New Zealand rest of Asia Africa Latin America and the Middle East</t>
         </is>
       </c>
       <c r="J10" s="53" t="n"/>
@@ -4500,10 +4525,10 @@
         </is>
       </c>
       <c r="G11" s="118" t="n">
-        <v>0.33</v>
+        <v>0.329</v>
       </c>
       <c r="H11" s="124" t="n">
-        <v>57507.32</v>
+        <v>67232.17</v>
       </c>
       <c r="I11" s="125" t="inlineStr">
         <is>
@@ -4513,7 +4538,7 @@
       <c r="J11" s="54" t="n"/>
       <c r="K11" s="28" t="n"/>
     </row>
-    <row r="12" ht="70" customHeight="1">
+    <row r="12" ht="52" customHeight="1">
       <c r="A12" s="36" t="n"/>
       <c r="B12" s="126" t="inlineStr">
         <is>
@@ -4522,39 +4547,39 @@
       </c>
       <c r="C12" s="115" t="inlineStr">
         <is>
-          <t>WAB</t>
+          <t>VTR</t>
         </is>
       </c>
       <c r="D12" s="116" t="inlineStr">
         <is>
-          <t>Westinghouse Air Brake Technologies Corporation</t>
+          <t>Ventas Inc.</t>
         </is>
       </c>
       <c r="E12" s="117" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F12" s="117" t="inlineStr">
         <is>
-          <t>Machinery</t>
+          <t>Health Care REITs</t>
         </is>
       </c>
       <c r="G12" s="118" t="n">
-        <v>0.326</v>
+        <v>0.317</v>
       </c>
       <c r="H12" s="119" t="n">
-        <v>43435.03</v>
+        <v>49034.35</v>
       </c>
       <c r="I12" s="120" t="inlineStr">
         <is>
-          <t>Westinghouse Air Brake Technologies Corporation provides locomotives equipment systems and services for the freight rail and passenger transit industries worldwide</t>
+          <t>Ventas Inc is an S&amp;P 500 company enabling exceptional environments that benefit a large and growing aging population</t>
         </is>
       </c>
       <c r="J12" s="53" t="n"/>
       <c r="K12" s="36" t="n"/>
     </row>
-    <row r="13" ht="106" customHeight="1">
+    <row r="13" ht="88" customHeight="1">
       <c r="A13" s="28" t="n"/>
       <c r="B13" s="126" t="inlineStr">
         <is>
@@ -4563,12 +4588,12 @@
       </c>
       <c r="C13" s="121" t="inlineStr">
         <is>
-          <t>FRT</t>
+          <t>KIM</t>
         </is>
       </c>
       <c r="D13" s="122" t="inlineStr">
         <is>
-          <t>Federal Realty Investment Trust</t>
+          <t>Kimco Realty Corporation</t>
         </is>
       </c>
       <c r="E13" s="123" t="inlineStr">
@@ -4582,14 +4607,14 @@
         </is>
       </c>
       <c r="G13" s="118" t="n">
-        <v>0.289</v>
+        <v>0.308</v>
       </c>
       <c r="H13" s="124" t="n">
-        <v>10799.18</v>
+        <v>17903.06</v>
       </c>
       <c r="I13" s="125" t="inlineStr">
         <is>
-          <t>Federal Realty Investment Trust is a recognized leader in the ownership operation and redevelopment of high-quality retail-based properties located primarily in major coastal markets and select underserved regions with strong economic and demographic fundamentals</t>
+          <t>Kimco Realty Corporation is a real estate investment trust (REIT) and leading owner and operator of high-quality open-air grocery-anchored shopping centers and mixed-use properties in the United States</t>
         </is>
       </c>
       <c r="J13" s="54" t="n"/>
@@ -4604,33 +4629,33 @@
       </c>
       <c r="C14" s="115" t="inlineStr">
         <is>
-          <t>NSC</t>
+          <t>FRT</t>
         </is>
       </c>
       <c r="D14" s="116" t="inlineStr">
         <is>
-          <t>Norfolk Southern Corporation</t>
+          <t>Federal Realty Investment Trust</t>
         </is>
       </c>
       <c r="E14" s="117" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F14" s="117" t="inlineStr">
         <is>
-          <t>Ground Transportation</t>
+          <t>Retail REITs</t>
         </is>
       </c>
       <c r="G14" s="118" t="n">
-        <v>0.233</v>
+        <v>0.292</v>
       </c>
       <c r="H14" s="119" t="n">
-        <v>69486.00999999999</v>
+        <v>11052.19</v>
       </c>
       <c r="I14" s="120" t="inlineStr">
         <is>
-          <t>Norfolk Southern Corporation together with its subsidiaries engages in the rail transportation of raw materials intermediate products and finished goods in the United States</t>
+          <t>Federal Realty Investment Trust is a recognized leader in the ownership operation and redevelopment of high-quality retail-based properties</t>
         </is>
       </c>
       <c r="J14" s="53" t="n"/>
@@ -4645,33 +4670,33 @@
       </c>
       <c r="C15" s="121" t="inlineStr">
         <is>
-          <t>ABBV</t>
+          <t>WAB</t>
         </is>
       </c>
       <c r="D15" s="122" t="inlineStr">
         <is>
-          <t>AbbVie Inc.</t>
+          <t>Westinghouse Air Brake Technologies Corporation</t>
         </is>
       </c>
       <c r="E15" s="123" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F15" s="123" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Machinery</t>
         </is>
       </c>
       <c r="G15" s="118" t="n">
-        <v>0.215</v>
+        <v>0.292</v>
       </c>
       <c r="H15" s="124" t="n">
-        <v>398482.45</v>
+        <v>50386.28</v>
       </c>
       <c r="I15" s="125" t="inlineStr">
         <is>
-          <t>AbbVie Inc a research-based biopharmaceutical company engages in the research and development manufacturing commercializing and sale of medicines and therapies worldwide</t>
+          <t>Westinghouse Air Brake Technologies Corporation provides locomotives equipment systems and services for the freight rail and passenger transit industries worldwide</t>
         </is>
       </c>
       <c r="J15" s="54" t="n"/>
@@ -4686,39 +4711,39 @@
       </c>
       <c r="C16" s="115" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>DGX</t>
         </is>
       </c>
       <c r="D16" s="116" t="inlineStr">
         <is>
-          <t>JPMorgan Chase &amp; Co.</t>
+          <t>Quest Diagnostics Incorporated</t>
         </is>
       </c>
       <c r="E16" s="117" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F16" s="117" t="inlineStr">
         <is>
-          <t>Banks</t>
+          <t>Health Care Providers and Services</t>
         </is>
       </c>
       <c r="G16" s="118" t="n">
-        <v>0.203</v>
+        <v>0.279</v>
       </c>
       <c r="H16" s="119" t="n">
-        <v>834204.25</v>
+        <v>25502.21</v>
       </c>
       <c r="I16" s="120" t="inlineStr">
         <is>
-          <t>JPMorgan Chase &amp; Co</t>
+          <t>Quest Diagnostics Incorporated provides diagnostic testing and services in the United States</t>
         </is>
       </c>
       <c r="J16" s="53" t="n"/>
       <c r="K16" s="36" t="n"/>
     </row>
-    <row r="17" ht="70" customHeight="1">
+    <row r="17" ht="52" customHeight="1">
       <c r="A17" s="28" t="n"/>
       <c r="B17" s="126" t="inlineStr">
         <is>
@@ -4727,33 +4752,33 @@
       </c>
       <c r="C17" s="121" t="inlineStr">
         <is>
-          <t>INCY</t>
+          <t>SPG</t>
         </is>
       </c>
       <c r="D17" s="122" t="inlineStr">
         <is>
-          <t>Incyte Corporation</t>
+          <t>Simon Property Group Inc.</t>
         </is>
       </c>
       <c r="E17" s="123" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F17" s="123" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Retail REITs</t>
         </is>
       </c>
       <c r="G17" s="118" t="n">
-        <v>0.182</v>
+        <v>0.245</v>
       </c>
       <c r="H17" s="124" t="n">
-        <v>21073.82</v>
+        <v>87858.7</v>
       </c>
       <c r="I17" s="125" t="inlineStr">
         <is>
-          <t>Incyte Corporation a biopharmaceutical company engages in the discovery development and commercialization of therapeutics in the United States Europe Canada and Japan</t>
+          <t>Simon Property Group Inc is a self-administered and self-managed real estate investment trust (REIT)</t>
         </is>
       </c>
       <c r="J17" s="54" t="n"/>
@@ -4761,101 +4786,101 @@
     </row>
     <row r="18" ht="70" customHeight="1">
       <c r="A18" s="36" t="n"/>
-      <c r="B18" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B18" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C18" s="115" t="inlineStr">
         <is>
-          <t>MPC</t>
+          <t>NSC</t>
         </is>
       </c>
       <c r="D18" s="116" t="inlineStr">
         <is>
-          <t>Marathon Petroleum Corporation</t>
+          <t>Norfolk Southern Corporation</t>
         </is>
       </c>
       <c r="E18" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F18" s="117" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Ground Transportation</t>
         </is>
       </c>
       <c r="G18" s="118" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.191</v>
       </c>
       <c r="H18" s="119" t="n">
-        <v>77721.12</v>
+        <v>76545.41</v>
       </c>
       <c r="I18" s="120" t="inlineStr">
         <is>
-          <t>Marathon Petroleum Corporation together with its subsidiaries operates as an integrated downstream energy company in the United States</t>
+          <t>Norfolk Southern Corporation together with its subsidiaries engages in the rail transportation of raw materials intermediate products and finished goods in the United States</t>
         </is>
       </c>
       <c r="J18" s="53" t="n"/>
       <c r="K18" s="36" t="n"/>
     </row>
-    <row r="19" ht="52" customHeight="1">
+    <row r="19" ht="70" customHeight="1">
       <c r="A19" s="28" t="n"/>
-      <c r="B19" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B19" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C19" s="121" t="inlineStr">
         <is>
-          <t>STT</t>
+          <t>ABBV</t>
         </is>
       </c>
       <c r="D19" s="122" t="inlineStr">
         <is>
-          <t>State Street Corporation</t>
+          <t>AbbVie Inc.</t>
         </is>
       </c>
       <c r="E19" s="123" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F19" s="123" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="G19" s="118" t="n">
-        <v>0.475</v>
+        <v>0.189</v>
       </c>
       <c r="H19" s="124" t="n">
-        <v>44725.83</v>
+        <v>455592.26</v>
       </c>
       <c r="I19" s="125" t="inlineStr">
         <is>
-          <t>State Street Corporation provides various financial products and services to institutional investors</t>
+          <t>AbbVie Inc a research-based biopharmaceutical company engages in the research and development manufacturing commercializing and sale of medicines and therapies worldwide</t>
         </is>
       </c>
       <c r="J19" s="54" t="n"/>
       <c r="K19" s="28" t="n"/>
     </row>
-    <row r="20" ht="52" customHeight="1">
+    <row r="20" ht="70" customHeight="1">
       <c r="A20" s="36" t="n"/>
-      <c r="B20" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B20" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C20" s="115" t="inlineStr">
         <is>
-          <t>CVS</t>
+          <t>INCY</t>
         </is>
       </c>
       <c r="D20" s="116" t="inlineStr">
         <is>
-          <t>CVS Health Corporation</t>
+          <t>Incyte Corporation</t>
         </is>
       </c>
       <c r="E20" s="117" t="inlineStr">
@@ -4865,38 +4890,38 @@
       </c>
       <c r="F20" s="117" t="inlineStr">
         <is>
-          <t>Health Care Providers and Services</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="G20" s="118" t="n">
-        <v>0.46</v>
+        <v>0.178</v>
       </c>
       <c r="H20" s="119" t="n">
-        <v>125211.85</v>
+        <v>23859.58</v>
       </c>
       <c r="I20" s="120" t="inlineStr">
         <is>
-          <t>CVS Health Corporation provides health solutions in the United States</t>
+          <t>Incyte Corporation a biopharmaceutical company engages in the discovery development and commercialization of therapeutics in the United States Europe Canada and Japan</t>
         </is>
       </c>
       <c r="J20" s="53" t="n"/>
       <c r="K20" s="36" t="n"/>
     </row>
-    <row r="21" ht="106" customHeight="1">
+    <row r="21" ht="70" customHeight="1">
       <c r="A21" s="28" t="n"/>
-      <c r="B21" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B21" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C21" s="121" t="inlineStr">
         <is>
-          <t>TRV</t>
+          <t>AIZ</t>
         </is>
       </c>
       <c r="D21" s="122" t="inlineStr">
         <is>
-          <t>The Travelers Companies Inc.</t>
+          <t>Assurant Inc.</t>
         </is>
       </c>
       <c r="E21" s="123" t="inlineStr">
@@ -4910,61 +4935,61 @@
         </is>
       </c>
       <c r="G21" s="118" t="n">
-        <v>0.39</v>
+        <v>0.173</v>
       </c>
       <c r="H21" s="124" t="n">
-        <v>64533.41</v>
+        <v>13786.88</v>
       </c>
       <c r="I21" s="125" t="inlineStr">
         <is>
-          <t>The Travelers Companies Inc through its subsidiaries provides a range of commercial and personal property and casualty insurance products and services to businesses government units associations and individuals in the United States Canada and internationally</t>
+          <t>Assurant Inc provides protection services to connected devices homes and automobiles in North America Latin America Europe and the Asia Pacific</t>
         </is>
       </c>
       <c r="J21" s="54" t="n"/>
       <c r="K21" s="28" t="n"/>
     </row>
-    <row r="22" ht="70" customHeight="1">
+    <row r="22" ht="52" customHeight="1">
       <c r="A22" s="36" t="n"/>
-      <c r="B22" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B22" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C22" s="115" t="inlineStr">
         <is>
-          <t>WELL</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="D22" s="116" t="inlineStr">
         <is>
-          <t>Welltower Inc.</t>
+          <t>JPMorgan Chase &amp; Co.</t>
         </is>
       </c>
       <c r="E22" s="117" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F22" s="117" t="inlineStr">
         <is>
-          <t>Health Care REITs</t>
+          <t>Banks</t>
         </is>
       </c>
       <c r="G22" s="118" t="n">
-        <v>0.37</v>
+        <v>0.171</v>
       </c>
       <c r="H22" s="119" t="n">
-        <v>148209.56</v>
+        <v>945144.28</v>
       </c>
       <c r="I22" s="120" t="inlineStr">
         <is>
-          <t>Welltower Inc is a S&amp;P 500 company is positioned at the center of the silver economy focusing on rental housing for aging seniors across the United States United Kingdom and Canada</t>
+          <t>JPMorgan Chase &amp; Co</t>
         </is>
       </c>
       <c r="J22" s="53" t="n"/>
       <c r="K22" s="36" t="n"/>
     </row>
-    <row r="23" ht="34" customHeight="1">
+    <row r="23" ht="52" customHeight="1">
       <c r="A23" s="28" t="n"/>
       <c r="B23" s="127" t="inlineStr">
         <is>
@@ -4973,33 +4998,33 @@
       </c>
       <c r="C23" s="121" t="inlineStr">
         <is>
-          <t>BBY</t>
+          <t>DVA</t>
         </is>
       </c>
       <c r="D23" s="122" t="inlineStr">
         <is>
-          <t>Best Buy Co. Inc.</t>
+          <t>DaVita Inc.</t>
         </is>
       </c>
       <c r="E23" s="123" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F23" s="123" t="inlineStr">
         <is>
-          <t>Specialty Retail</t>
+          <t>Health Care Providers and Services</t>
         </is>
       </c>
       <c r="G23" s="118" t="n">
-        <v>0.357</v>
+        <v>1.203</v>
       </c>
       <c r="H23" s="124" t="n">
-        <v>16078.79</v>
+        <v>15188.76</v>
       </c>
       <c r="I23" s="125" t="inlineStr">
         <is>
-          <t>Best Buy Co</t>
+          <t>DaVita Inc provides kidney dialysis services for patients suffering from chronic kidney failure in the United States</t>
         </is>
       </c>
       <c r="J23" s="54" t="n"/>
@@ -5014,39 +5039,39 @@
       </c>
       <c r="C24" s="115" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>MPC</t>
         </is>
       </c>
       <c r="D24" s="116" t="inlineStr">
         <is>
-          <t>The Bank of New York Mellon Corporation</t>
+          <t>Marathon Petroleum Corporation</t>
         </is>
       </c>
       <c r="E24" s="117" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F24" s="117" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G24" s="118" t="n">
-        <v>0.351</v>
+        <v>0.797</v>
       </c>
       <c r="H24" s="119" t="n">
-        <v>96186.41</v>
+        <v>91152.84</v>
       </c>
       <c r="I24" s="120" t="inlineStr">
         <is>
-          <t>The Bank of New York Mellon Corporation provides a range of financial products and services in the United States and internationally</t>
+          <t>Marathon Petroleum Corporation together with its subsidiaries operates as an integrated downstream energy company in the United States</t>
         </is>
       </c>
       <c r="J24" s="53" t="n"/>
       <c r="K24" s="36" t="n"/>
     </row>
-    <row r="25" ht="70" customHeight="1">
+    <row r="25" ht="52" customHeight="1">
       <c r="A25" s="28" t="n"/>
       <c r="B25" s="127" t="inlineStr">
         <is>
@@ -5055,39 +5080,39 @@
       </c>
       <c r="C25" s="121" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>CVS</t>
         </is>
       </c>
       <c r="D25" s="122" t="inlineStr">
         <is>
-          <t>Union Pacific Corporation</t>
+          <t>CVS Health Corporation</t>
         </is>
       </c>
       <c r="E25" s="123" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F25" s="123" t="inlineStr">
         <is>
-          <t>Ground Transportation</t>
+          <t>Health Care Providers and Services</t>
         </is>
       </c>
       <c r="G25" s="118" t="n">
-        <v>0.35</v>
+        <v>0.47</v>
       </c>
       <c r="H25" s="124" t="n">
-        <v>158667.48</v>
+        <v>137372.71</v>
       </c>
       <c r="I25" s="125" t="inlineStr">
         <is>
-          <t>Union Pacific Corporation through its subsidiary Union Pacific Railroad Company operates in the railroad business in the United States</t>
+          <t>CVS Health Corporation provides health solutions in the United States</t>
         </is>
       </c>
       <c r="J25" s="54" t="n"/>
       <c r="K25" s="28" t="n"/>
     </row>
-    <row r="26" ht="70" customHeight="1">
+    <row r="26" ht="52" customHeight="1">
       <c r="A26" s="36" t="n"/>
       <c r="B26" s="127" t="inlineStr">
         <is>
@@ -5096,39 +5121,39 @@
       </c>
       <c r="C26" s="115" t="inlineStr">
         <is>
-          <t>DOC</t>
+          <t>STT</t>
         </is>
       </c>
       <c r="D26" s="116" t="inlineStr">
         <is>
-          <t>Healthpeak Properties Inc.</t>
+          <t>State Street Corporation</t>
         </is>
       </c>
       <c r="E26" s="117" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F26" s="117" t="inlineStr">
         <is>
-          <t>Health Care REITs</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="G26" s="118" t="n">
-        <v>0.345</v>
+        <v>0.415</v>
       </c>
       <c r="H26" s="119" t="n">
-        <v>14353.95</v>
+        <v>50462.03</v>
       </c>
       <c r="I26" s="120" t="inlineStr">
         <is>
-          <t>Healthpeak Properties Inc is a Standard &amp; Poor’s 500 company that owns operates and develops high-quality real estate focused on healthcare discovery and delivery in the United States</t>
+          <t>State Street Corporation provides various financial products and services to institutional investors</t>
         </is>
       </c>
       <c r="J26" s="53" t="n"/>
       <c r="K26" s="36" t="n"/>
     </row>
-    <row r="27" ht="52" customHeight="1">
+    <row r="27" ht="34" customHeight="1">
       <c r="A27" s="28" t="n"/>
       <c r="B27" s="127" t="inlineStr">
         <is>
@@ -5137,39 +5162,39 @@
       </c>
       <c r="C27" s="121" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>BBY</t>
         </is>
       </c>
       <c r="D27" s="122" t="inlineStr">
         <is>
-          <t>Apple Inc.</t>
+          <t>Best Buy Co. Inc.</t>
         </is>
       </c>
       <c r="E27" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F27" s="123" t="inlineStr">
         <is>
-          <t>Technology Hardware Storage and Peripherals</t>
+          <t>Specialty Retail</t>
         </is>
       </c>
       <c r="G27" s="118" t="n">
-        <v>0.311</v>
+        <v>0.401</v>
       </c>
       <c r="H27" s="124" t="n">
-        <v>4309578.68</v>
+        <v>18710.64</v>
       </c>
       <c r="I27" s="125" t="inlineStr">
         <is>
-          <t>Apple Inc designs manufactures and markets smartphones personal computers tablets wearables and accessories worldwide</t>
+          <t>Best Buy Co</t>
         </is>
       </c>
       <c r="J27" s="54" t="n"/>
       <c r="K27" s="28" t="n"/>
     </row>
-    <row r="28" ht="88" customHeight="1">
+    <row r="28" ht="106" customHeight="1">
       <c r="A28" s="36" t="n"/>
       <c r="B28" s="127" t="inlineStr">
         <is>
@@ -5178,39 +5203,39 @@
       </c>
       <c r="C28" s="115" t="inlineStr">
         <is>
-          <t>ADM</t>
+          <t>TRV</t>
         </is>
       </c>
       <c r="D28" s="116" t="inlineStr">
         <is>
-          <t>Archer-Daniels-Midland Company</t>
+          <t>The Travelers Companies Inc.</t>
         </is>
       </c>
       <c r="E28" s="117" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F28" s="117" t="inlineStr">
         <is>
-          <t>Food Products</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="G28" s="118" t="n">
-        <v>0.26</v>
+        <v>0.382</v>
       </c>
       <c r="H28" s="119" t="n">
-        <v>39380.19</v>
+        <v>81399.95</v>
       </c>
       <c r="I28" s="120" t="inlineStr">
         <is>
-          <t>Archer-Daniels-Midland Company provides human and animal nutrition ingredients and solutions in the United States Switzerland the Cayman Islands Brazil Mexico Canada the United Kingdom and internationally</t>
+          <t>The Travelers Companies Inc through its subsidiaries provides a range of commercial and personal property and casualty insurance products and services to businesses government units associations and individuals in the United States Canada and internationally</t>
         </is>
       </c>
       <c r="J28" s="53" t="n"/>
       <c r="K28" s="36" t="n"/>
     </row>
-    <row r="29" ht="88" customHeight="1">
+    <row r="29" ht="52" customHeight="1">
       <c r="A29" s="28" t="n"/>
       <c r="B29" s="127" t="inlineStr">
         <is>
@@ -5219,33 +5244,33 @@
       </c>
       <c r="C29" s="121" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>DOC</t>
         </is>
       </c>
       <c r="D29" s="122" t="inlineStr">
         <is>
-          <t>Bank of America Corporation</t>
+          <t>Healthpeak Properties Inc.</t>
         </is>
       </c>
       <c r="E29" s="123" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F29" s="123" t="inlineStr">
         <is>
-          <t>Banks</t>
+          <t>Health Care REITs</t>
         </is>
       </c>
       <c r="G29" s="118" t="n">
-        <v>0.225</v>
+        <v>0.355</v>
       </c>
       <c r="H29" s="124" t="n">
-        <v>388502.86</v>
+        <v>15755.27</v>
       </c>
       <c r="I29" s="125" t="inlineStr">
         <is>
-          <t>Bank of America Corporation through its subsidiaries provides various financial products and services for individual consumers small and middle-market businesses institutional investors large corporations and governments worldwide</t>
+          <t>Healthpeak Properties Inc is a fully integrated real estate investment trust (REIT) and S&amp;P 500 company</t>
         </is>
       </c>
       <c r="J29" s="54" t="n"/>
@@ -5260,33 +5285,33 @@
       </c>
       <c r="C30" s="115" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>WELL</t>
         </is>
       </c>
       <c r="D30" s="116" t="inlineStr">
         <is>
-          <t>Everest Group Ltd.</t>
+          <t>Welltower Inc.</t>
         </is>
       </c>
       <c r="E30" s="117" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F30" s="117" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Health Care REITs</t>
         </is>
       </c>
       <c r="G30" s="118" t="n">
-        <v>0.21</v>
+        <v>0.353</v>
       </c>
       <c r="H30" s="119" t="n">
-        <v>13320.91</v>
+        <v>176578.15</v>
       </c>
       <c r="I30" s="120" t="inlineStr">
         <is>
-          <t>Everest Group Ltd together with subsidiaries provides reinsurance and insurance products in the United States Europe and internationally</t>
+          <t>Welltower Inc an S&amp;P 500 company is positioned at the center of the silver economy focusing on rental housing for aging seniors across the United States United Kingdom and Canada</t>
         </is>
       </c>
       <c r="J30" s="53" t="n"/>
@@ -5301,12 +5326,12 @@
       </c>
       <c r="C31" s="121" t="inlineStr">
         <is>
-          <t>PRU</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="D31" s="122" t="inlineStr">
         <is>
-          <t>Prudential Financial Inc.</t>
+          <t>The Bank of New York Mellon Corporation</t>
         </is>
       </c>
       <c r="E31" s="123" t="inlineStr">
@@ -5316,24 +5341,24 @@
       </c>
       <c r="F31" s="123" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="G31" s="118" t="n">
-        <v>0.157</v>
+        <v>0.306</v>
       </c>
       <c r="H31" s="124" t="n">
-        <v>36717.82</v>
+        <v>107234.16</v>
       </c>
       <c r="I31" s="125" t="inlineStr">
         <is>
-          <t>Prudential Financial Inc together with its subsidiaries provides financial products and services in the United States Japan and internationally</t>
+          <t>The Bank of New York Mellon Corporation provides a range of financial products and services in the United States and internationally</t>
         </is>
       </c>
       <c r="J31" s="54" t="n"/>
       <c r="K31" s="28" t="n"/>
     </row>
-    <row r="32" ht="34" customHeight="1">
+    <row r="32" ht="52" customHeight="1">
       <c r="A32" s="36" t="n"/>
       <c r="B32" s="127" t="inlineStr">
         <is>
@@ -5342,33 +5367,33 @@
       </c>
       <c r="C32" s="115" t="inlineStr">
         <is>
-          <t>IVZ</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="D32" s="116" t="inlineStr">
         <is>
-          <t>Invesco Ltd.</t>
+          <t>Apple Inc.</t>
         </is>
       </c>
       <c r="E32" s="117" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F32" s="117" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Technology Hardware Storage and Peripherals</t>
         </is>
       </c>
       <c r="G32" s="118" t="n">
-        <v>0.127</v>
+        <v>0.302</v>
       </c>
       <c r="H32" s="119" t="n">
-        <v>12167.61</v>
+        <v>4930986.03</v>
       </c>
       <c r="I32" s="120" t="inlineStr">
         <is>
-          <t>Invesco Ltd is a publicly owned investment manager</t>
+          <t>Apple Inc designs manufactures and markets smartphones personal computers tablets wearables and accessories worldwide</t>
         </is>
       </c>
       <c r="J32" s="53" t="n"/>
@@ -5376,19 +5401,19 @@
     </row>
     <row r="33" ht="70" customHeight="1">
       <c r="A33" s="28" t="n"/>
-      <c r="B33" s="128" t="inlineStr">
-        <is>
-          <t>STRK</t>
+      <c r="B33" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C33" s="121" t="inlineStr">
         <is>
-          <t>CSX</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="D33" s="122" t="inlineStr">
         <is>
-          <t>CSX Corporation</t>
+          <t>Union Pacific Corporation</t>
         </is>
       </c>
       <c r="E33" s="123" t="inlineStr">
@@ -5402,234 +5427,514 @@
         </is>
       </c>
       <c r="G33" s="118" t="n">
-        <v>0.41</v>
+        <v>0.294</v>
       </c>
       <c r="H33" s="124" t="n">
-        <v>86617.14</v>
+        <v>176506.37</v>
       </c>
       <c r="I33" s="125" t="inlineStr">
         <is>
-          <t>CSX Corporation together with its subsidiaries provides rail-based freight transportation services in the United States and Canada</t>
+          <t>Union Pacific Corporation through its subsidiary Union Pacific Railroad Company operates in the railroad business in the United States</t>
         </is>
       </c>
       <c r="J33" s="54" t="n"/>
       <c r="K33" s="28" t="n"/>
     </row>
-    <row r="34" ht="70" customHeight="1">
+    <row r="34" ht="34" customHeight="1">
       <c r="A34" s="36" t="n"/>
-      <c r="B34" s="129" t="inlineStr">
-        <is>
-          <t>STRK</t>
-        </is>
-      </c>
-      <c r="C34" s="147" t="inlineStr">
-        <is>
-          <t>MET</t>
-        </is>
-      </c>
-      <c r="D34" s="148" t="inlineStr">
-        <is>
-          <t>MetLife Inc.</t>
-        </is>
-      </c>
-      <c r="E34" s="149" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F34" s="149" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="G34" s="133" t="n">
-        <v>0.269</v>
-      </c>
-      <c r="H34" s="150" t="n">
-        <v>55851.6</v>
-      </c>
-      <c r="I34" s="151" t="inlineStr">
-        <is>
-          <t>MetLife Inc a financial services company provides insurance annuities employee benefits and asset management services worldwide</t>
+      <c r="B34" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C34" s="115" t="inlineStr">
+        <is>
+          <t>GWW</t>
+        </is>
+      </c>
+      <c r="D34" s="116" t="inlineStr">
+        <is>
+          <t>W.W. Grainger Inc.</t>
+        </is>
+      </c>
+      <c r="E34" s="117" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="F34" s="117" t="inlineStr">
+        <is>
+          <t>Trading Companies and Distributors</t>
+        </is>
+      </c>
+      <c r="G34" s="118" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="H34" s="119" t="n">
+        <v>65761.08</v>
+      </c>
+      <c r="I34" s="120" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J34" s="53" t="n"/>
       <c r="K34" s="36" t="n"/>
     </row>
-    <row r="35" ht="8" customHeight="1">
+    <row r="35" ht="70" customHeight="1">
       <c r="A35" s="28" t="n"/>
-      <c r="B35" s="136" t="n"/>
-      <c r="C35" s="137" t="n"/>
-      <c r="D35" s="138" t="n"/>
-      <c r="E35" s="139" t="n"/>
-      <c r="F35" s="139" t="n"/>
-      <c r="G35" s="140" t="n"/>
-      <c r="H35" s="141" t="n"/>
-      <c r="I35" s="142" t="n"/>
+      <c r="B35" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C35" s="121" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="D35" s="122" t="inlineStr">
+        <is>
+          <t>Block Inc.</t>
+        </is>
+      </c>
+      <c r="E35" s="123" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F35" s="123" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="G35" s="118" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H35" s="124" t="n">
+        <v>48278.54</v>
+      </c>
+      <c r="I35" s="125" t="inlineStr">
+        <is>
+          <t>Block Inc together with its subsidiaries builds ecosystems focused on commerce and financial products and services in the United States and internationally</t>
+        </is>
+      </c>
       <c r="J35" s="54" t="n"/>
       <c r="K35" s="28" t="n"/>
     </row>
-    <row r="36" ht="34" customHeight="1">
+    <row r="36" ht="88" customHeight="1">
       <c r="A36" s="36" t="n"/>
-      <c r="B36" s="143" t="inlineStr">
-        <is>
-          <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
-        </is>
-      </c>
-      <c r="C36" s="144" t="n"/>
-      <c r="D36" s="144" t="n"/>
-      <c r="E36" s="144" t="n"/>
-      <c r="F36" s="144" t="n"/>
-      <c r="G36" s="144" t="n"/>
-      <c r="H36" s="144" t="n"/>
-      <c r="I36" s="144" t="n"/>
+      <c r="B36" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C36" s="115" t="inlineStr">
+        <is>
+          <t>ADM</t>
+        </is>
+      </c>
+      <c r="D36" s="116" t="inlineStr">
+        <is>
+          <t>Archer-Daniels-Midland Company</t>
+        </is>
+      </c>
+      <c r="E36" s="117" t="inlineStr">
+        <is>
+          <t>Consumer Staples</t>
+        </is>
+      </c>
+      <c r="F36" s="117" t="inlineStr">
+        <is>
+          <t>Food Products</t>
+        </is>
+      </c>
+      <c r="G36" s="118" t="n">
+        <v>0.262</v>
+      </c>
+      <c r="H36" s="119" t="n">
+        <v>40086.25</v>
+      </c>
+      <c r="I36" s="120" t="inlineStr">
+        <is>
+          <t>Archer-Daniels-Midland Company provides human and animal nutrition ingredients and solutions in the United States Switzerland the Cayman Islands Brazil Mexico Canada the United Kingdom and internationally</t>
+        </is>
+      </c>
       <c r="J36" s="53" t="n"/>
       <c r="K36" s="36" t="n"/>
     </row>
-    <row r="37" ht="28" customHeight="1">
+    <row r="37" ht="70" customHeight="1">
       <c r="A37" s="28" t="n"/>
-      <c r="B37" s="145" t="inlineStr">
-        <is>
-          <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
-        </is>
-      </c>
-      <c r="C37" s="146" t="n"/>
-      <c r="D37" s="146" t="n"/>
-      <c r="E37" s="146" t="n"/>
-      <c r="F37" s="146" t="n"/>
-      <c r="G37" s="146" t="n"/>
-      <c r="H37" s="146" t="n"/>
-      <c r="I37" s="146" t="n"/>
+      <c r="B37" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C37" s="121" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D37" s="122" t="inlineStr">
+        <is>
+          <t>Everest Group Ltd.</t>
+        </is>
+      </c>
+      <c r="E37" s="123" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F37" s="123" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="G37" s="118" t="n">
+        <v>0.194</v>
+      </c>
+      <c r="H37" s="124" t="n">
+        <v>15393</v>
+      </c>
+      <c r="I37" s="125" t="inlineStr">
+        <is>
+          <t>Everest Group Ltd together with subsidiaries provides reinsurance and insurance products in the United States Europe and internationally</t>
+        </is>
+      </c>
       <c r="J37" s="54" t="n"/>
       <c r="K37" s="28" t="n"/>
     </row>
-    <row r="38" ht="20.4" customHeight="1">
+    <row r="38" ht="88" customHeight="1">
       <c r="A38" s="36" t="n"/>
-      <c r="B38" s="48" t="n"/>
-      <c r="C38" s="38" t="n"/>
-      <c r="D38" s="39" t="n"/>
-      <c r="E38" s="40" t="n"/>
-      <c r="F38" s="40" t="n"/>
-      <c r="G38" s="89" t="n"/>
-      <c r="H38" s="91" t="n"/>
-      <c r="I38" s="53" t="n"/>
+      <c r="B38" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C38" s="115" t="inlineStr">
+        <is>
+          <t>BAC</t>
+        </is>
+      </c>
+      <c r="D38" s="116" t="inlineStr">
+        <is>
+          <t>Bank of America Corporation</t>
+        </is>
+      </c>
+      <c r="E38" s="117" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F38" s="117" t="inlineStr">
+        <is>
+          <t>Banks</t>
+        </is>
+      </c>
+      <c r="G38" s="118" t="n">
+        <v>0.183</v>
+      </c>
+      <c r="H38" s="119" t="n">
+        <v>436335.11</v>
+      </c>
+      <c r="I38" s="120" t="inlineStr">
+        <is>
+          <t>Bank of America Corporation through its subsidiaries provides various financial products and services for individual consumers small and middle-market businesses institutional investors large corporations and governments worldwide</t>
+        </is>
+      </c>
       <c r="J38" s="53" t="n"/>
       <c r="K38" s="36" t="n"/>
     </row>
-    <row r="39" ht="24" customHeight="1">
+    <row r="39" ht="106" customHeight="1">
       <c r="A39" s="28" t="n"/>
-      <c r="B39" s="49" t="n"/>
-      <c r="C39" s="30" t="n"/>
-      <c r="D39" s="31" t="n"/>
-      <c r="E39" s="32" t="n"/>
-      <c r="F39" s="32" t="n"/>
-      <c r="G39" s="89" t="n"/>
-      <c r="H39" s="93" t="n"/>
-      <c r="I39" s="54" t="n"/>
+      <c r="B39" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C39" s="121" t="inlineStr">
+        <is>
+          <t>PAYX</t>
+        </is>
+      </c>
+      <c r="D39" s="122" t="inlineStr">
+        <is>
+          <t>Paychex Inc.</t>
+        </is>
+      </c>
+      <c r="E39" s="123" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="F39" s="123" t="inlineStr">
+        <is>
+          <t>Professional Services</t>
+        </is>
+      </c>
+      <c r="G39" s="118" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="H39" s="124" t="n">
+        <v>41283.4</v>
+      </c>
+      <c r="I39" s="125" t="inlineStr">
+        <is>
+          <t>Paychex Inc together with its subsidiaries provides human capital management solutions (HCM) for human resources payroll processing employee benefits and insurance services for small to medium-sized businesses in the United States Europe Canada India and Israel</t>
+        </is>
+      </c>
       <c r="J39" s="54" t="n"/>
       <c r="K39" s="28" t="n"/>
     </row>
-    <row r="40" ht="24" customHeight="1">
+    <row r="40" ht="70" customHeight="1">
       <c r="A40" s="36" t="n"/>
-      <c r="B40" s="48" t="n"/>
-      <c r="C40" s="38" t="n"/>
-      <c r="D40" s="39" t="n"/>
-      <c r="E40" s="40" t="n"/>
-      <c r="F40" s="40" t="n"/>
-      <c r="G40" s="89" t="n"/>
-      <c r="H40" s="91" t="n"/>
-      <c r="I40" s="53" t="n"/>
+      <c r="B40" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C40" s="115" t="inlineStr">
+        <is>
+          <t>PRU</t>
+        </is>
+      </c>
+      <c r="D40" s="116" t="inlineStr">
+        <is>
+          <t>Prudential Financial Inc.</t>
+        </is>
+      </c>
+      <c r="E40" s="117" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F40" s="117" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="G40" s="118" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="H40" s="119" t="n">
+        <v>42168.74</v>
+      </c>
+      <c r="I40" s="120" t="inlineStr">
+        <is>
+          <t>Prudential Financial Inc together with its subsidiaries provides financial products and services in the United States Japan and internationally</t>
+        </is>
+      </c>
       <c r="J40" s="53" t="n"/>
       <c r="K40" s="36" t="n"/>
     </row>
-    <row r="41" ht="30.6" customHeight="1">
+    <row r="41" ht="34" customHeight="1">
       <c r="A41" s="28" t="n"/>
-      <c r="B41" s="49" t="n"/>
-      <c r="C41" s="30" t="n"/>
-      <c r="D41" s="31" t="n"/>
-      <c r="E41" s="32" t="n"/>
-      <c r="F41" s="32" t="n"/>
-      <c r="G41" s="89" t="n"/>
-      <c r="H41" s="93" t="n"/>
-      <c r="I41" s="54" t="n"/>
+      <c r="B41" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C41" s="121" t="inlineStr">
+        <is>
+          <t>IVZ</t>
+        </is>
+      </c>
+      <c r="D41" s="122" t="inlineStr">
+        <is>
+          <t>Invesco Ltd.</t>
+        </is>
+      </c>
+      <c r="E41" s="123" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F41" s="123" t="inlineStr">
+        <is>
+          <t>Capital Markets</t>
+        </is>
+      </c>
+      <c r="G41" s="118" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H41" s="124" t="n">
+        <v>13256.34</v>
+      </c>
+      <c r="I41" s="125" t="inlineStr">
+        <is>
+          <t>Invesco Ltd is a publicly owned investment manager</t>
+        </is>
+      </c>
       <c r="J41" s="54" t="n"/>
       <c r="K41" s="28" t="n"/>
     </row>
-    <row r="42" ht="24.6" customHeight="1" thickBot="1">
+    <row r="42" ht="52" customHeight="1" thickBot="1">
       <c r="A42" s="75" t="n"/>
-      <c r="B42" s="76" t="n"/>
-      <c r="C42" s="77" t="n"/>
-      <c r="D42" s="78" t="n"/>
-      <c r="E42" s="79" t="n"/>
-      <c r="F42" s="79" t="n"/>
-      <c r="G42" s="94" t="n"/>
-      <c r="H42" s="105" t="n"/>
-      <c r="I42" s="81" t="n"/>
+      <c r="B42" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C42" s="115" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="D42" s="116" t="inlineStr">
+        <is>
+          <t>Visa Inc.</t>
+        </is>
+      </c>
+      <c r="E42" s="117" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F42" s="117" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="G42" s="118" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="H42" s="119" t="n">
+        <v>682683.01</v>
+      </c>
+      <c r="I42" s="120" t="inlineStr">
+        <is>
+          <t>Visa Inc operates as a payment technology company in the United States and internationally</t>
+        </is>
+      </c>
       <c r="J42" s="81" t="n"/>
       <c r="K42" s="75" t="n"/>
     </row>
-    <row r="43">
+    <row r="43" ht="70" customHeight="1">
       <c r="A43" s="43" t="n"/>
-      <c r="B43" s="43" t="n"/>
-      <c r="C43" s="43" t="n"/>
-      <c r="D43" s="43" t="n"/>
-      <c r="E43" s="43" t="n"/>
-      <c r="F43" s="43" t="n"/>
-      <c r="G43" s="43" t="n"/>
-      <c r="H43" s="43" t="n"/>
-      <c r="I43" s="43" t="n"/>
+      <c r="B43" s="128" t="inlineStr">
+        <is>
+          <t>STRK</t>
+        </is>
+      </c>
+      <c r="C43" s="121" t="inlineStr">
+        <is>
+          <t>CSX</t>
+        </is>
+      </c>
+      <c r="D43" s="122" t="inlineStr">
+        <is>
+          <t>CSX Corporation</t>
+        </is>
+      </c>
+      <c r="E43" s="123" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="F43" s="123" t="inlineStr">
+        <is>
+          <t>Ground Transportation</t>
+        </is>
+      </c>
+      <c r="G43" s="118" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="H43" s="124" t="n">
+        <v>95620</v>
+      </c>
+      <c r="I43" s="125" t="inlineStr">
+        <is>
+          <t>CSX Corporation together with its subsidiaries provides rail-based freight transportation services in the United States and Canada</t>
+        </is>
+      </c>
       <c r="J43" s="43" t="n"/>
       <c r="K43" s="43" t="n"/>
     </row>
-    <row r="44" ht="15.6" customHeight="1" thickBot="1">
+    <row r="44" ht="70" customHeight="1" thickBot="1">
       <c r="A44" s="43" t="n"/>
-      <c r="B44" s="43" t="n"/>
-      <c r="C44" s="43" t="n"/>
-      <c r="D44" s="43" t="n"/>
-      <c r="E44" s="43" t="n"/>
-      <c r="F44" s="43" t="n"/>
-      <c r="G44" s="43" t="n"/>
-      <c r="H44" s="43" t="n"/>
-      <c r="I44" s="43" t="n"/>
+      <c r="B44" s="129" t="inlineStr">
+        <is>
+          <t>STRK</t>
+        </is>
+      </c>
+      <c r="C44" s="147" t="inlineStr">
+        <is>
+          <t>MET</t>
+        </is>
+      </c>
+      <c r="D44" s="148" t="inlineStr">
+        <is>
+          <t>MetLife Inc.</t>
+        </is>
+      </c>
+      <c r="E44" s="149" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F44" s="149" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="G44" s="133" t="n">
+        <v>0.233</v>
+      </c>
+      <c r="H44" s="150" t="n">
+        <v>61293.14</v>
+      </c>
+      <c r="I44" s="151" t="inlineStr">
+        <is>
+          <t>MetLife Inc a financial services company provides insurance annuities employee benefits and asset management services worldwide</t>
+        </is>
+      </c>
       <c r="J44" s="43" t="n"/>
       <c r="K44" s="43" t="n"/>
     </row>
-    <row r="45" ht="10.2" customHeight="1">
+    <row r="45" ht="8" customHeight="1">
       <c r="A45" s="43" t="n"/>
-      <c r="B45" s="58" t="n"/>
-      <c r="C45" s="59" t="n"/>
-      <c r="D45" s="59" t="n"/>
-      <c r="E45" s="59" t="n"/>
-      <c r="F45" s="59" t="n"/>
-      <c r="G45" s="59" t="n"/>
-      <c r="H45" s="59" t="n"/>
-      <c r="I45" s="60" t="n"/>
+      <c r="B45" s="152" t="n"/>
+      <c r="C45" s="152" t="n"/>
+      <c r="D45" s="152" t="n"/>
+      <c r="E45" s="152" t="n"/>
+      <c r="F45" s="152" t="n"/>
+      <c r="G45" s="152" t="n"/>
+      <c r="H45" s="152" t="n"/>
+      <c r="I45" s="152" t="n"/>
       <c r="J45" s="60" t="n"/>
       <c r="K45" s="43" t="n"/>
     </row>
-    <row r="46" ht="15.6" customHeight="1">
+    <row r="46" ht="34" customHeight="1">
       <c r="A46" s="43" t="n"/>
-      <c r="B46" s="67" t="n"/>
-      <c r="C46" s="64" t="n"/>
-      <c r="D46" s="64" t="n"/>
-      <c r="E46" s="64" t="n"/>
-      <c r="F46" s="64" t="n"/>
-      <c r="G46" s="64" t="n"/>
-      <c r="H46" s="64" t="n"/>
-      <c r="I46" s="65" t="n"/>
+      <c r="B46" s="143" t="inlineStr">
+        <is>
+          <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
+        </is>
+      </c>
+      <c r="C46" s="144" t="n"/>
+      <c r="D46" s="144" t="n"/>
+      <c r="E46" s="144" t="n"/>
+      <c r="F46" s="144" t="n"/>
+      <c r="G46" s="144" t="n"/>
+      <c r="H46" s="144" t="n"/>
+      <c r="I46" s="144" t="n"/>
       <c r="J46" s="65" t="n"/>
       <c r="K46" s="43" t="n"/>
     </row>
-    <row r="47" ht="10.8" customHeight="1" thickBot="1">
+    <row r="47" ht="28" customHeight="1" thickBot="1">
       <c r="A47" s="43" t="n"/>
-      <c r="B47" s="61" t="n"/>
-      <c r="C47" s="62" t="n"/>
-      <c r="D47" s="62" t="n"/>
-      <c r="E47" s="62" t="n"/>
-      <c r="F47" s="62" t="n"/>
-      <c r="G47" s="62" t="n"/>
-      <c r="H47" s="62" t="n"/>
-      <c r="I47" s="63" t="n"/>
+      <c r="B47" s="145" t="inlineStr">
+        <is>
+          <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
+        </is>
+      </c>
+      <c r="C47" s="146" t="n"/>
+      <c r="D47" s="146" t="n"/>
+      <c r="E47" s="146" t="n"/>
+      <c r="F47" s="146" t="n"/>
+      <c r="G47" s="146" t="n"/>
+      <c r="H47" s="146" t="n"/>
+      <c r="I47" s="146" t="n"/>
       <c r="J47" s="63" t="n"/>
       <c r="K47" s="43" t="n"/>
     </row>
@@ -5663,11 +5968,11 @@
   <mergeCells count="5">
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B36:I36"/>
-    <mergeCell ref="B37:I37"/>
+    <mergeCell ref="B47:I47"/>
+    <mergeCell ref="B46:I46"/>
     <mergeCell ref="B6:G6"/>
   </mergeCells>
-  <conditionalFormatting sqref="G8:G34">
+  <conditionalFormatting sqref="G8:G44">
     <cfRule type="colorScale" priority="1351">
       <colorScale>
         <cfvo type="min"/>
